--- a/ig/nr-changes/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-changes/StructureDefinition-as-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$152</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5042" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4916" uniqueCount="611">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T15:25:16+00:00</t>
+    <t>2023-05-03T15:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1660,45 +1660,45 @@
     <t>Extension</t>
   </si>
   <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
     <t>Valeurs possibles :
 ORG pour une BAL organisationnelle;
 APP pour une BAL applicative;
 PER pour une BAL personnelle, rattachée à une personne physique</t>
   </si>
   <si>
+    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
     <t>Type de  boîte aux lettre MSS</t>
   </si>
   <si>
@@ -1744,15 +1744,15 @@
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.value[x]</t>
   </si>
   <si>
-    <t>Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
-  </si>
-  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service</t>
   </si>
   <si>
     <t>service</t>
   </si>
   <si>
+    <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
+  </si>
+  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
   </si>
   <si>
@@ -1765,15 +1765,6 @@
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.value[x]</t>
   </si>
   <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
-  </si>
-  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone</t>
   </si>
   <si>
@@ -1795,18 +1786,16 @@
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.value[x]</t>
   </si>
   <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté</t>
-  </si>
-  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization</t>
   </si>
   <si>
     <t>digitization</t>
   </si>
   <si>
+    <t>Indicateur d’acceptation de la dématérialisation (ou « Zéro papier »). - O : Dématérialisation acceptée 
+- N : Dématérialisation refusée</t>
+  </si>
+  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.id</t>
   </si>
   <si>
@@ -1819,25 +1808,16 @@
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.value[x]</t>
   </si>
   <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.value[x]:valueBoolean</t>
-  </si>
-  <si>
-    <t>valueBoolean</t>
-  </si>
-  <si>
-    <t>Indicateur d’acceptation de la dématérialisation (ou « Zéro papier »</t>
-  </si>
-  <si>
-    <t>- O : Dématérialisation acceptée 
-- N : Dématérialisation refusée</t>
-  </si>
-  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication</t>
   </si>
   <si>
     <t>publication</t>
   </si>
   <si>
+    <t>Indicateur liste rouge. O: Boîte aux lettres en liste rouge;
+N: La boîte aux lettres peut être publiée</t>
+  </si>
+  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.id</t>
   </si>
   <si>
@@ -1848,16 +1828,6 @@
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.value[x]:valueBoolean</t>
-  </si>
-  <si>
-    <t>ndicateur liste rouge</t>
-  </si>
-  <si>
-    <t>O: Boîte aux lettres en liste rouge;
-N: La boîte aux lettres peut être publiée</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
@@ -2259,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ156"/>
+  <dimension ref="A1:AJ152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="118.80859375" customWidth="true" bestFit="true"/>
@@ -13521,7 +13491,7 @@
         <v>525</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13589,10 +13559,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13691,10 +13661,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13789,13 +13759,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="B113" t="s" s="2">
-        <v>534</v>
-      </c>
       <c r="C113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>71</v>
@@ -13823,7 +13793,7 @@
         <v>164</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>537</v>
+        <v>165</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13925,7 +13895,7 @@
         <v>525</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14125,7 +14095,7 @@
         <v>525</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14196,7 +14166,7 @@
         <v>543</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14298,7 +14268,7 @@
         <v>544</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14429,7 +14399,7 @@
         <v>548</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14629,7 +14599,7 @@
         <v>525</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -14700,7 +14670,7 @@
         <v>551</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14802,7 +14772,7 @@
         <v>552</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14828,7 +14798,7 @@
         <v>146</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>553</v>
+        <v>164</v>
       </c>
       <c r="M123" t="s" s="2">
         <v>165</v>
@@ -14899,13 +14869,13 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>522</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>71</v>
@@ -14930,10 +14900,10 @@
         <v>123</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -15133,7 +15103,7 @@
         <v>525</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15204,7 +15174,7 @@
         <v>558</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15244,7 +15214,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>71</v>
@@ -15306,7 +15276,7 @@
         <v>559</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15374,14 +15344,16 @@
         <v>71</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AC128" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD128" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="AF128" t="s" s="2">
         <v>168</v>
@@ -15404,7 +15376,7 @@
         <v>560</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>561</v>
@@ -15429,13 +15401,13 @@
         <v>71</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>562</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>165</v>
+        <v>531</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -15486,19 +15458,19 @@
         <v>71</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="130" hidden="true">
@@ -15506,11 +15478,9 @@
         <v>563</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>71</v>
       </c>
@@ -15531,13 +15501,13 @@
         <v>71</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>565</v>
+        <v>147</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>526</v>
+        <v>148</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15588,27 +15558,27 @@
         <v>71</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15619,7 +15589,7 @@
         <v>72</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>71</v>
@@ -15631,13 +15601,13 @@
         <v>71</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>147</v>
+        <v>525</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>148</v>
+        <v>531</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -15676,39 +15646,39 @@
         <v>71</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15716,10 +15686,10 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>71</v>
@@ -15731,22 +15701,24 @@
         <v>71</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>525</v>
+        <v>156</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>71</v>
+        <v>561</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>71</v>
@@ -15776,39 +15748,39 @@
         <v>71</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15816,7 +15788,7 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>78</v>
@@ -15831,24 +15803,22 @@
         <v>71</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
-        <v>564</v>
+        <v>71</v>
       </c>
       <c r="S133" t="s" s="2">
         <v>71</v>
@@ -15890,29 +15860,31 @@
         <v>71</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C134" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="D134" t="s" s="2">
         <v>71</v>
       </c>
@@ -15933,13 +15905,13 @@
         <v>71</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>164</v>
+        <v>569</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>165</v>
+        <v>531</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15978,29 +15950,31 @@
         <v>71</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AC134" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD134" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="135" hidden="true">
@@ -16008,11 +15982,9 @@
         <v>570</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
         <v>71</v>
       </c>
@@ -16036,10 +16008,10 @@
         <v>146</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>571</v>
+        <v>147</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -16090,7 +16062,7 @@
         <v>71</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>72</v>
@@ -16099,22 +16071,20 @@
         <v>78</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C136" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>71</v>
       </c>
@@ -16123,7 +16093,7 @@
         <v>72</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>71</v>
@@ -16141,7 +16111,7 @@
         <v>525</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -16180,16 +16150,16 @@
         <v>71</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF136" t="s" s="2">
         <v>153</v>
@@ -16209,10 +16179,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16220,7 +16190,7 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>78</v>
@@ -16235,22 +16205,24 @@
         <v>71</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>71</v>
@@ -16292,10 +16264,10 @@
         <v>71</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>78</v>
@@ -16309,10 +16281,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16323,7 +16295,7 @@
         <v>72</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>71</v>
@@ -16335,13 +16307,13 @@
         <v>71</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>123</v>
+        <v>259</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>525</v>
+        <v>164</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>526</v>
+        <v>165</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -16380,47 +16352,49 @@
         <v>71</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C139" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="D139" t="s" s="2">
         <v>71</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>78</v>
@@ -16435,24 +16409,22 @@
         <v>71</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>156</v>
+        <v>576</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>573</v>
+        <v>71</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>71</v>
@@ -16494,19 +16466,19 @@
         <v>71</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="140" hidden="true">
@@ -16514,7 +16486,7 @@
         <v>577</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16537,13 +16509,13 @@
         <v>71</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -16582,17 +16554,19 @@
         <v>71</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AC140" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD140" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>72</v>
@@ -16601,10 +16575,10 @@
         <v>78</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="141" hidden="true">
@@ -16612,11 +16586,9 @@
         <v>578</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>71</v>
       </c>
@@ -16625,7 +16597,7 @@
         <v>72</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>71</v>
@@ -16637,17 +16609,15 @@
         <v>71</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>259</v>
+        <v>123</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>580</v>
+        <v>525</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>71</v>
@@ -16684,49 +16654,47 @@
         <v>71</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C142" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
         <v>71</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>78</v>
@@ -16741,22 +16709,24 @@
         <v>71</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>525</v>
+        <v>156</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N142" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q142" s="2"/>
       <c r="R142" t="s" s="2">
-        <v>71</v>
+        <v>575</v>
       </c>
       <c r="S142" t="s" s="2">
         <v>71</v>
@@ -16798,27 +16768,27 @@
         <v>71</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16841,13 +16811,13 @@
         <v>71</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>146</v>
+        <v>259</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16898,7 +16868,7 @@
         <v>71</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>72</v>
@@ -16907,18 +16877,18 @@
         <v>78</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>530</v>
+        <v>582</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16926,10 +16896,10 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>71</v>
@@ -16941,22 +16911,24 @@
         <v>71</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>525</v>
+        <v>156</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N144" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>71</v>
+        <v>583</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>71</v>
@@ -16986,39 +16958,39 @@
         <v>71</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>532</v>
+        <v>585</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17026,10 +16998,10 @@
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>71</v>
@@ -17041,24 +17013,22 @@
         <v>71</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>93</v>
+        <v>586</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>583</v>
+        <v>71</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>71</v>
@@ -17100,19 +17070,19 @@
         <v>71</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="146" hidden="true">
@@ -17120,7 +17090,7 @@
         <v>587</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>534</v>
+        <v>588</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17128,7 +17098,7 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>78</v>
@@ -17140,18 +17110,20 @@
         <v>71</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>164</v>
+        <v>407</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N146" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>71</v>
@@ -17161,7 +17133,7 @@
         <v>71</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>71</v>
+        <v>589</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>71</v>
@@ -17176,29 +17148,31 @@
         <v>71</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>71</v>
+        <v>218</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>71</v>
+        <v>410</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>71</v>
+        <v>411</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AC146" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD146" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE146" t="s" s="2">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>168</v>
+        <v>412</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>72</v>
@@ -17207,7 +17181,7 @@
         <v>78</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>90</v>
+        <v>413</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>91</v>
@@ -17215,46 +17189,46 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C147" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
         <v>71</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>165</v>
+        <v>416</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O147" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>71</v>
       </c>
@@ -17302,7 +17276,7 @@
         <v>71</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>72</v>
@@ -17319,10 +17293,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17330,7 +17304,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>78</v>
@@ -17339,30 +17313,32 @@
         <v>71</v>
       </c>
       <c r="I148" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>156</v>
+        <v>421</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>157</v>
+        <v>422</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O148" s="2"/>
+        <v>595</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q148" s="2"/>
       <c r="R148" t="s" s="2">
-        <v>593</v>
+        <v>71</v>
       </c>
       <c r="S148" t="s" s="2">
         <v>71</v>
@@ -17380,13 +17356,13 @@
         <v>71</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>71</v>
+        <v>218</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>71</v>
+        <v>425</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>71</v>
+        <v>426</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>71</v>
@@ -17404,27 +17380,27 @@
         <v>71</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>160</v>
+        <v>427</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17435,7 +17411,7 @@
         <v>72</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>71</v>
@@ -17444,18 +17420,20 @@
         <v>71</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>596</v>
+        <v>429</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>164</v>
+        <v>430</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N149" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>71</v>
@@ -17504,7 +17482,7 @@
         <v>71</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>168</v>
+        <v>433</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>72</v>
@@ -17521,10 +17499,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17532,7 +17510,7 @@
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>78</v>
@@ -17547,16 +17525,16 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>313</v>
+        <v>437</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -17567,7 +17545,7 @@
         <v>71</v>
       </c>
       <c r="S150" t="s" s="2">
-        <v>599</v>
+        <v>71</v>
       </c>
       <c r="T150" t="s" s="2">
         <v>71</v>
@@ -17582,13 +17560,13 @@
         <v>71</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>218</v>
+        <v>71</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>410</v>
+        <v>71</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>411</v>
+        <v>71</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>71</v>
@@ -17606,7 +17584,7 @@
         <v>71</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>72</v>
@@ -17615,10 +17593,10 @@
         <v>78</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>413</v>
+        <v>90</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>91</v>
+        <v>250</v>
       </c>
     </row>
     <row r="151" hidden="true">
@@ -17626,7 +17604,7 @@
         <v>600</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17634,34 +17612,34 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G151" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>146</v>
+        <v>601</v>
       </c>
       <c r="L151" t="s" s="2">
         <v>602</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>417</v>
+        <v>603</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>418</v>
+        <v>604</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>71</v>
@@ -17710,7 +17688,7 @@
         <v>71</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>419</v>
+        <v>600</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>72</v>
@@ -17727,10 +17705,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17741,31 +17719,31 @@
         <v>72</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I152" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>99</v>
+        <v>606</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>421</v>
+        <v>607</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>422</v>
+        <v>608</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>424</v>
+        <v>610</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>71</v>
@@ -17790,13 +17768,13 @@
         <v>71</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>218</v>
+        <v>71</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>425</v>
+        <v>71</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>426</v>
+        <v>71</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>71</v>
@@ -17814,435 +17792,23 @@
         <v>71</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>427</v>
+        <v>605</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O153" s="2"/>
-      <c r="P153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="154" hidden="true">
-      <c r="A154" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O154" s="2"/>
-      <c r="P154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="155" hidden="true">
-      <c r="A155" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="P155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="156" hidden="true">
-      <c r="A156" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="P156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
         <v>257</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ156">
+  <autoFilter ref="A1:AJ152">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18252,7 +17818,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI155">
+  <conditionalFormatting sqref="A2:AI151">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/nr-changes/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-changes/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T15:57:05+00:00</t>
+    <t>2023-05-03T16:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-changes/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-changes/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T16:01:19+00:00</t>
+    <t>2023-05-03T16:12:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
